--- a/exports/HINDUNILVR_full_report.xlsx
+++ b/exports/HINDUNILVR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>2319.5</v>
+        <v>2266.2</v>
       </c>
       <c r="I2" t="n">
         <v>2310.6416461273</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.62</v>
+        <v>-3.88</v>
       </c>
       <c r="L2" t="n">
-        <v>2.43</v>
+        <v>3.96</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N2" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O2" t="n">
         <v>-0.33</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.85</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44609.55208333334</v>
+        <v>44610.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2253.3</v>
+        <v>2277.3</v>
       </c>
       <c r="I3" t="n">
         <v>2261.088728679402</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>0.57</v>
+        <v>-0.49</v>
       </c>
       <c r="L3" t="n">
         <v>2.45</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>4.15</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2213.3</v>
+        <v>2176.8</v>
       </c>
       <c r="I4" t="n">
         <v>2192.930699302988</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.81</v>
+        <v>-4.41</v>
       </c>
       <c r="L4" t="n">
-        <v>3.08</v>
+        <v>5.41</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44</v>
+        <v>2.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.18</v>
+        <v>3.96</v>
       </c>
       <c r="O4" t="n">
         <v>0.42</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>3.77</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1967.7</v>
+        <v>2039.6</v>
       </c>
       <c r="I5" t="n">
         <v>2010.884615135015</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>9.609999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.03</v>
       </c>
       <c r="M5" t="n">
-        <v>1.29</v>
+        <v>2.29</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>4.74</v>
       </c>
       <c r="O5" t="n">
         <v>-3.96</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.61</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44642.55208333334</v>
+        <v>44643.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1954.7</v>
+        <v>1943.2</v>
       </c>
       <c r="I6" t="n">
         <v>1947.607705629508</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.16</v>
+        <v>-4.73</v>
       </c>
       <c r="L6" t="n">
         <v>5.3</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.52</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2006.9</v>
+        <v>2023.2</v>
       </c>
       <c r="I7" t="n">
         <v>2007.997482350567</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.28</v>
+        <v>-4.12</v>
       </c>
       <c r="L7" t="n">
-        <v>3.68</v>
+        <v>4.29</v>
       </c>
       <c r="M7" t="n">
         <v>0.97</v>
       </c>
       <c r="N7" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
         <v>-0.72</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44676.38541666666</v>
+        <v>44676.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2068.5</v>
+        <v>2066</v>
       </c>
       <c r="I8" t="n">
         <v>2066.379718444873</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="L8" t="n">
         <v>1.17</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.2</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44679.55208333334</v>
+        <v>44680.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2194.3</v>
+        <v>2237.2</v>
       </c>
       <c r="I9" t="n">
         <v>2211.985144024115</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.21</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>6.82</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>4.18</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.13</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2232.5</v>
+        <v>2175.6</v>
       </c>
       <c r="I10" t="n">
         <v>2208.361060626358</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.21</v>
+        <v>-2.75</v>
       </c>
       <c r="L10" t="n">
         <v>7.65</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.51</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44735.38541666666</v>
+        <v>44735.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>2186.8</v>
+        <v>2207</v>
       </c>
       <c r="I11" t="n">
         <v>2188.341061378202</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.51</v>
+        <v>-1.44</v>
       </c>
       <c r="L11" t="n">
         <v>1.88</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.25</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44796.38541666666</v>
+        <v>44796.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>2552.2</v>
+        <v>2545.4</v>
       </c>
       <c r="I12" t="n">
         <v>2548.25485534516</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>60.83333333333334</v>
+        <v>61</v>
       </c>
       <c r="K12" t="n">
-        <v>15.64</v>
+        <v>15.33</v>
       </c>
       <c r="L12" t="n">
         <v>1.97</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>3.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2572.4</v>
+        <v>2620.5</v>
       </c>
       <c r="I13" t="n">
         <v>2575.690699839477</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.06</v>
+        <v>-2.95</v>
       </c>
       <c r="L13" t="n">
-        <v>2.78</v>
+        <v>3.32</v>
       </c>
       <c r="M13" t="n">
         <v>0.96</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>4.92</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44841.55208333334</v>
+        <v>44844.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2545.4</v>
+        <v>2542</v>
       </c>
       <c r="I14" t="n">
         <v>2542.254814420876</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.87</v>
+        <v>-3</v>
       </c>
       <c r="L14" t="n">
-        <v>3.61</v>
+        <v>4.85</v>
       </c>
       <c r="M14" t="n">
-        <v>0.38</v>
+        <v>0.96</v>
       </c>
       <c r="N14" t="n">
         <v>2.92</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>3.94</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44888.55208333334</v>
+        <v>44889.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2459.1</v>
+        <v>2488.1</v>
       </c>
       <c r="I15" t="n">
         <v>2486.202044061249</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K15" t="n">
-        <v>3.26</v>
+        <v>2.12</v>
       </c>
       <c r="L15" t="n">
         <v>2.9</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.51</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2591.5</v>
+        <v>2572.4</v>
       </c>
       <c r="I16" t="n">
         <v>2583.335229108515</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>4.16</v>
+        <v>3.39</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>4</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44935.38541666666</v>
+        <v>44935.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2546.7</v>
+        <v>2570.5</v>
       </c>
       <c r="I17" t="n">
         <v>2564.903171625166</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>1.03</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.95</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44945.55208333334</v>
+        <v>44946.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2592.6</v>
+        <v>2508.9</v>
       </c>
       <c r="I18" t="n">
         <v>2537.520477946343</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>0.86</v>
+        <v>-2.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.37</v>
+        <v>3.52</v>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>3.52</v>
       </c>
       <c r="O18" t="n">
         <v>1.58</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45005.38541666666</v>
+        <v>45005.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2413</v>
+        <v>2461</v>
       </c>
       <c r="I19" t="n">
         <v>2434.264823180611</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>3.82</v>
+        <v>1.91</v>
       </c>
       <c r="L19" t="n">
         <v>3.9</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.76</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45042.55208333334</v>
+        <v>45043.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2467</v>
+        <v>2422.3</v>
       </c>
       <c r="I20" t="n">
         <v>2424.486503750718</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>0.24</v>
+        <v>-1.57</v>
       </c>
       <c r="L20" t="n">
         <v>2.17</v>
@@ -1581,7 +1820,7 @@
         <v>0.89</v>
       </c>
       <c r="N20" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
         <v>2.2</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>4.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45055.55208333334</v>
+        <v>45056.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2466</v>
+        <v>2480.6</v>
       </c>
       <c r="I21" t="n">
         <v>2471.576449940022</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8</v>
+        <v>-2.41</v>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
         <v>0.5600000000000001</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45070.55208333334</v>
+        <v>45071.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2565.4</v>
+        <v>2537.3</v>
       </c>
       <c r="I22" t="n">
         <v>2542.25214795276</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>3.42</v>
+        <v>2.29</v>
       </c>
       <c r="L22" t="n">
         <v>0.91</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>3.64</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2616.7</v>
+        <v>2647.7</v>
       </c>
       <c r="I23" t="n">
         <v>2617.179297064806</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.13</v>
+        <v>-4.35</v>
       </c>
       <c r="L23" t="n">
-        <v>3.61</v>
+        <v>5.59</v>
       </c>
       <c r="M23" t="n">
         <v>0.66</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.43</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2626.5</v>
+        <v>2576.9</v>
       </c>
       <c r="I24" t="n">
         <v>2585.963281471437</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8</v>
+        <v>-2.67</v>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
         <v>0.11</v>
       </c>
       <c r="N24" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="O24" t="n">
         <v>0.88</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.83</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45111.55208333334</v>
+        <v>45112.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2650</v>
+        <v>2687.7</v>
       </c>
       <c r="I25" t="n">
         <v>2668.628976859281</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.84</v>
+        <v>-4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>3.69</v>
+        <v>4.49</v>
       </c>
       <c r="M25" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>1.08</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>-1.41</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>3.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2647.4</v>
+        <v>2621.6</v>
       </c>
       <c r="I26" t="n">
         <v>2628.645160062455</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5</v>
+        <v>-2.46</v>
       </c>
       <c r="L26" t="n">
-        <v>1.79</v>
+        <v>2.78</v>
       </c>
       <c r="M26" t="n">
         <v>0.06</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.06</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45156.55208333334</v>
+        <v>45159.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2506.9</v>
+        <v>2518.8</v>
       </c>
       <c r="I27" t="n">
         <v>2517.31429709482</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>4.38</v>
+        <v>3.92</v>
       </c>
       <c r="L27" t="n">
         <v>1.65</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45168.55208333334</v>
+        <v>45169.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2484</v>
+        <v>2465.4</v>
       </c>
       <c r="I28" t="n">
         <v>2473.604056221011</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.38</v>
+        <v>-2.12</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="M28" t="n">
         <v>0.18</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>2.9</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2468.3</v>
+        <v>2509.7</v>
       </c>
       <c r="I29" t="n">
         <v>2473.180008497203</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.12</v>
+        <v>-1.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
         <v>0.85</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>3.48</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2501.3</v>
+        <v>2438.6</v>
       </c>
       <c r="I30" t="n">
         <v>2453.67638898939</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.33</v>
+        <v>-2.83</v>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>2.87</v>
       </c>
       <c r="M30" t="n">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="N30" t="n">
-        <v>0.47</v>
+        <v>1.92</v>
       </c>
       <c r="O30" t="n">
         <v>1.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>4.27</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45259.55208333334</v>
+        <v>45260.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2476.9</v>
+        <v>2493.3</v>
       </c>
       <c r="I31" t="n">
         <v>2485.71471423399</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.57</v>
+        <v>-2.24</v>
       </c>
       <c r="L31" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>2.59</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2522.9</v>
+        <v>2471</v>
       </c>
       <c r="I32" t="n">
         <v>2482.209146046021</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>1.19</v>
+        <v>-0.89</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
-        <v>0.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>1.48</v>
+        <v>1.92</v>
       </c>
       <c r="O32" t="n">
         <v>0.63</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>3.97</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45281.55208333334</v>
+        <v>45282.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2504.2</v>
+        <v>2522.4</v>
       </c>
       <c r="I33" t="n">
         <v>2520.628989259734</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.34</v>
+        <v>-2.08</v>
       </c>
       <c r="L33" t="n">
         <v>2.42</v>
@@ -2322,7 +2717,7 @@
         <v>0.51</v>
       </c>
       <c r="N33" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="O33" t="n">
         <v>-1.92</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>3.14</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45296.55208333334</v>
+        <v>45299.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2570</v>
+        <v>2517.5</v>
       </c>
       <c r="I34" t="n">
         <v>2540.599364464953</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>1.89</v>
+        <v>-0.19</v>
       </c>
       <c r="L34" t="n">
         <v>0.96</v>
@@ -2379,7 +2786,7 @@
         <v>0.61</v>
       </c>
       <c r="N34" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="O34" t="n">
         <v>0.9</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2393.4</v>
+        <v>2442.5</v>
       </c>
       <c r="I35" t="n">
         <v>2436.632650740866</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>4.93</v>
+        <v>2.98</v>
       </c>
       <c r="L35" t="n">
         <v>2.32</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>5.08</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2344.4</v>
+        <v>2331.1</v>
       </c>
       <c r="I36" t="n">
         <v>2341.077991800715</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.02</v>
+        <v>-4.56</v>
       </c>
       <c r="L36" t="n">
-        <v>4.42</v>
+        <v>4.7</v>
       </c>
       <c r="M36" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="N36" t="n">
         <v>1.53</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>3.17</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45351.55208333334</v>
+        <v>45352.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2358.9</v>
+        <v>2383.6</v>
       </c>
       <c r="I37" t="n">
         <v>2378.364344745185</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.19</v>
+        <v>-2.25</v>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M37" t="n">
         <v>0.68</v>
       </c>
       <c r="N37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="O37" t="n">
         <v>-0.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>3.33</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2334.4</v>
+        <v>2283.5</v>
       </c>
       <c r="I38" t="n">
         <v>2309.650377956795</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.06</v>
+        <v>-4.2</v>
       </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>4.36</v>
       </c>
       <c r="M38" t="n">
         <v>0.57</v>
       </c>
       <c r="N38" t="n">
-        <v>1.12</v>
+        <v>2.56</v>
       </c>
       <c r="O38" t="n">
         <v>1.05</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.15</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2203.1</v>
+        <v>2227.3</v>
       </c>
       <c r="I39" t="n">
         <v>2209.473111198577</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>3.52</v>
+        <v>2.46</v>
       </c>
       <c r="L39" t="n">
         <v>2.02</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>3.45</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45463.55208333334</v>
+        <v>45464.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2433.6</v>
+        <v>2389.3</v>
       </c>
       <c r="I40" t="n">
         <v>2404.674815412704</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K40" t="n">
-        <v>9.26</v>
+        <v>7.27</v>
       </c>
       <c r="L40" t="n">
         <v>2.94</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2450.2</v>
+        <v>2485.9</v>
       </c>
       <c r="I41" t="n">
         <v>2472.472380105189</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.55</v>
+        <v>-4.04</v>
       </c>
       <c r="L41" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="M41" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="O41" t="n">
         <v>-1.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>4.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2848.9</v>
+        <v>2797.5</v>
       </c>
       <c r="I42" t="n">
         <v>2837.831900266339</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>14.6</v>
+        <v>12.53</v>
       </c>
       <c r="L42" t="n">
         <v>1.51</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>5.71</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2393.4</v>
+        <v>2432.6</v>
       </c>
       <c r="I43" t="n">
         <v>2423.607313803439</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K43" t="n">
-        <v>14.45</v>
+        <v>13.04</v>
       </c>
       <c r="L43" t="n">
         <v>2.17</v>
       </c>
       <c r="M43" t="n">
-        <v>0.63</v>
+        <v>1.23</v>
       </c>
       <c r="N43" t="n">
         <v>2.35</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>4.07</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45637.55208333334</v>
+        <v>45638.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>2359.1</v>
+        <v>2304.2</v>
       </c>
       <c r="I44" t="n">
         <v>2350.829011228046</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.02</v>
+        <v>-5.28</v>
       </c>
       <c r="L44" t="n">
-        <v>3.9</v>
+        <v>5.43</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="N44" t="n">
         <v>3.34</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>2340.3</v>
+        <v>2357.1</v>
       </c>
       <c r="I45" t="n">
         <v>2346.583682189972</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.57</v>
+        <v>-2.3</v>
       </c>
       <c r="L45" t="n">
-        <v>2.17</v>
+        <v>2.79</v>
       </c>
       <c r="M45" t="n">
         <v>0.6</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>3.34</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2331.4</v>
+        <v>2298.8</v>
       </c>
       <c r="I46" t="n">
         <v>2306.423544235277</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.09</v>
+        <v>-2.47</v>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="M46" t="n">
         <v>0.9399999999999999</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.13</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45687.38541666666</v>
+        <v>45687.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>2354.5</v>
+        <v>2377.1</v>
       </c>
       <c r="I47" t="n">
         <v>2357.99594331493</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.42</v>
+        <v>-3.41</v>
       </c>
       <c r="L47" t="n">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="M47" t="n">
         <v>0.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.03</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45693.38541666666</v>
+        <v>45693.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>2364.9</v>
+        <v>2347.1</v>
       </c>
       <c r="I48" t="n">
         <v>2350.341306302965</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.51</v>
+        <v>-1.26</v>
       </c>
       <c r="L48" t="n">
-        <v>0.98</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
         <v>0.9</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.01</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2165.8</v>
+        <v>2216.2</v>
       </c>
       <c r="I49" t="n">
         <v>2196.092376157382</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>7.72</v>
+        <v>5.58</v>
       </c>
       <c r="L49" t="n">
         <v>0.82</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.83</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45771.38541666666</v>
+        <v>45771.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2287.9</v>
+        <v>2281.1</v>
       </c>
       <c r="I50" t="n">
         <v>2286.370884763356</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="L50" t="n">
         <v>4.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.43</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45842.38541666666</v>
+        <v>45842.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>2283.4</v>
+        <v>2296.4</v>
       </c>
       <c r="I51" t="n">
         <v>2289.04433817099</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>70.83333333333333</v>
+        <v>71</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1</v>
+        <v>-0.67</v>
       </c>
       <c r="L51" t="n">
         <v>3.61</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>2.62</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45861.55208333334</v>
+        <v>45862.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2408.8</v>
+        <v>2385.8</v>
       </c>
       <c r="I52" t="n">
         <v>2397.137425283454</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>4.89</v>
+        <v>3.89</v>
       </c>
       <c r="L52" t="n">
         <v>0.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>3.63</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2387.4</v>
+        <v>2481.9</v>
       </c>
       <c r="I53" t="n">
         <v>2437.834483289918</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="L53" t="n">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="M53" t="n">
         <v>0.24</v>
       </c>
       <c r="N53" t="n">
-        <v>0.91</v>
+        <v>3.74</v>
       </c>
       <c r="O53" t="n">
         <v>-0.84</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.34</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45911.55208333334</v>
+        <v>45912.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2576.5</v>
+        <v>2528.8</v>
       </c>
       <c r="I54" t="n">
         <v>2540.490795065851</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K54" t="n">
-        <v>3.81</v>
+        <v>1.89</v>
       </c>
       <c r="L54" t="n">
         <v>4.35</v>
@@ -3519,7 +4166,7 @@
         <v>0.57</v>
       </c>
       <c r="N54" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="O54" t="n">
         <v>3.74</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2511.1</v>
+        <v>2557.9</v>
       </c>
       <c r="I55" t="n">
         <v>2522.119640391308</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7</v>
+        <v>-1.15</v>
       </c>
       <c r="L55" t="n">
         <v>1.97</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45953.55208333334</v>
+        <v>45954.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2552.8</v>
+        <v>2465.4</v>
       </c>
       <c r="I56" t="n">
         <v>2486.212042254817</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.2</v>
+        <v>-3.62</v>
       </c>
       <c r="L56" t="n">
-        <v>1.83</v>
+        <v>5.11</v>
       </c>
       <c r="M56" t="n">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="N56" t="n">
-        <v>0.51</v>
+        <v>3.36</v>
       </c>
       <c r="O56" t="n">
         <v>1.7</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.55</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45989.38541666666</v>
+        <v>45989.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>2415</v>
+        <v>2422.5</v>
       </c>
       <c r="I57" t="n">
         <v>2415.535223326131</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="L57" t="n">
         <v>2.81</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>2.45</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2417</v>
+        <v>2330.2</v>
       </c>
       <c r="I58" t="n">
         <v>2375.093335286786</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.23</v>
+        <v>-3.81</v>
       </c>
       <c r="L58" t="n">
-        <v>2.7</v>
+        <v>5.61</v>
       </c>
       <c r="M58" t="n">
         <v>0.12</v>
       </c>
       <c r="N58" t="n">
-        <v>1.35</v>
+        <v>3.14</v>
       </c>
       <c r="O58" t="n">
         <v>0.6</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.64</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2325.1</v>
+        <v>2357.2</v>
       </c>
       <c r="I59" t="n">
         <v>2335.612485252636</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>0.22</v>
+        <v>-1.16</v>
       </c>
       <c r="L59" t="n">
         <v>4.71</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.26</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2386</v>
+        <v>2338.7</v>
       </c>
       <c r="I60" t="n">
         <v>2343.920440012876</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K60" t="n">
-        <v>1.22</v>
+        <v>-0.78</v>
       </c>
       <c r="L60" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="N60" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O60" t="n">
         <v>1.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.54</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46063.55208333334</v>
+        <v>46064.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2448.5</v>
+        <v>2460.1</v>
       </c>
       <c r="I61" t="n">
         <v>2452.906907607049</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.69</v>
+        <v>-5.19</v>
       </c>
       <c r="L61" t="n">
-        <v>5.11</v>
+        <v>5.64</v>
       </c>
       <c r="M61" t="n">
         <v>1.66</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>4.02</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46065.55208333334</v>
+        <v>46066.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2407</v>
+        <v>2324.8</v>
       </c>
       <c r="I62" t="n">
         <v>2370.601406711217</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.16</v>
+        <v>-5.5</v>
       </c>
       <c r="L62" t="n">
-        <v>4.47</v>
+        <v>5.74</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>0.29</v>
       </c>
       <c r="N62" t="n">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="O62" t="n">
         <v>0.38</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.14</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2115.2</v>
+        <v>2155</v>
       </c>
       <c r="I63" t="n">
         <v>2149.709945162012</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K63" t="n">
-        <v>9.02</v>
+        <v>7.3</v>
       </c>
       <c r="L63" t="n">
         <v>3.23</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.54</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46161.38541666666</v>
+        <v>46161.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>2253.9</v>
+        <v>2230.2</v>
       </c>
       <c r="I64" t="n">
         <v>2232.973123665932</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>4.59</v>
+        <v>3.49</v>
       </c>
       <c r="L64" t="n">
         <v>1.93</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.21</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2134.4</v>
+        <v>2184.9</v>
       </c>
       <c r="I65" t="n">
         <v>2170.991950912635</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>4.3</v>
+        <v>2.03</v>
       </c>
       <c r="L65" t="n">
         <v>1.21</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>2144.5</v>
+        <v>2120.9</v>
       </c>
       <c r="I66" t="n">
         <v>2127.196049981475</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.85</v>
+        <v>-2.93</v>
       </c>
       <c r="L66" t="n">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="M66" t="n">
         <v>1.21</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>4.25</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46204.55208333334</v>
+        <v>46205.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>2181.5</v>
+        <v>2204.7</v>
       </c>
       <c r="I67" t="n">
         <v>2195.453535037431</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.86</v>
+        <v>-3.95</v>
       </c>
       <c r="L67" t="n">
-        <v>3.26</v>
+        <v>4.11</v>
       </c>
       <c r="M67" t="n">
         <v>0.48</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.31</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>2166.9</v>
+        <v>2135.5</v>
       </c>
       <c r="I68" t="n">
         <v>2136.880082595747</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.71</v>
+        <v>-3.14</v>
       </c>
       <c r="L68" t="n">
-        <v>1.78</v>
+        <v>3.39</v>
       </c>
       <c r="M68" t="n">
         <v>0.19</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>4.44</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>2146.5</v>
+        <v>2176.6</v>
       </c>
       <c r="I69" t="n">
         <v>2174.884474335433</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.52</v>
+        <v>-1.92</v>
       </c>
       <c r="L69" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="M69" t="n">
         <v>0.5</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>3.5</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2173.6</v>
+        <v>2043.9</v>
       </c>
       <c r="I70" t="n">
         <v>2111.637716887222</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.14</v>
+        <v>-6.1</v>
       </c>
       <c r="L70" t="n">
-        <v>1.11</v>
+        <v>6.54</v>
       </c>
       <c r="M70" t="n">
         <v>-0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="O70" t="n">
         <v>1.26</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>9.26</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46309.38541666666</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>1889.2</v>
+        <v>1895</v>
       </c>
       <c r="I71" t="n">
         <v>1889.361385100282</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>78</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>7.57</v>
+        <v>7.29</v>
       </c>
       <c r="L71" t="n">
         <v>8.27</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>4</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1845</v>
+        <v>1822.8</v>
       </c>
       <c r="I72" t="n">
         <v>1827.837991712135</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.64</v>
+        <v>-3.81</v>
       </c>
       <c r="L72" t="n">
-        <v>3.27</v>
+        <v>4.25</v>
       </c>
       <c r="M72" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="N72" t="n">
         <v>1.55</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>10</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7590,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7600,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7610,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7620,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7630,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7640,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -6767,7 +7650,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -6777,7 +7660,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6787,7 +7670,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.8</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6797,7 +7680,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.06</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7690,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7700,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.12</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7710,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.64</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7720,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.7</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7730,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.67</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7740,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -6867,7 +7750,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.27</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6877,7 +7760,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -6897,7 +7780,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="25">
@@ -6917,7 +7800,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7810,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.93</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7820,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
